--- a/C题/p2_part2/p2b_三组预测对比.xlsx
+++ b/C题/p2_part2/p2b_三组预测对比.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -442,30 +442,50 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>gross</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>terminal_value</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>total</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>net_change</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>end_soc</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
         <is>
           <t>gapE</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>ngap</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>purchE</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>smin</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>smax</t>
         </is>
@@ -478,27 +498,39 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>12244924.02292138</v>
+        <v>12251652.55401508</v>
       </c>
       <c r="C2" t="n">
-        <v>3.024628957367289e-09</v>
+        <v>3.380970573137649e-09</v>
       </c>
       <c r="D2" t="n">
-        <v>12244924.02292138</v>
+        <v>12251652.55401508</v>
       </c>
       <c r="E2" t="n">
-        <v>4.716487940944114e-10</v>
+        <v>461.268</v>
       </c>
       <c r="F2" t="n">
-        <v>461</v>
+        <v>12251191.28601508</v>
       </c>
       <c r="G2" t="n">
-        <v>20218602.47691976</v>
+        <v>12253500.32601508</v>
       </c>
       <c r="H2" t="n">
         <v>1200</v>
       </c>
       <c r="I2" t="n">
+        <v>5.359197530196978e-10</v>
+      </c>
+      <c r="J2" t="n">
+        <v>491</v>
+      </c>
+      <c r="K2" t="n">
+        <v>20184246.76118428</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1199.999999999998</v>
+      </c>
+      <c r="M2" t="n">
         <v>10800</v>
       </c>
     </row>
@@ -509,27 +541,39 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>12250485.8841281</v>
+        <v>12254084.9438321</v>
       </c>
       <c r="C3" t="n">
-        <v>4136569.973593471</v>
+        <v>4133899.85498511</v>
       </c>
       <c r="D3" t="n">
-        <v>16387055.85772157</v>
+        <v>16387984.79881721</v>
       </c>
       <c r="E3" t="n">
-        <v>952616.3594999769</v>
+        <v>461.268</v>
       </c>
       <c r="F3" t="n">
-        <v>25451</v>
+        <v>16387523.53081721</v>
       </c>
       <c r="G3" t="n">
-        <v>20271187.93489057</v>
+        <v>16389832.57081721</v>
       </c>
       <c r="H3" t="n">
         <v>1200</v>
       </c>
       <c r="I3" t="n">
+        <v>953922.0299791532</v>
+      </c>
+      <c r="J3" t="n">
+        <v>25466</v>
+      </c>
+      <c r="K3" t="n">
+        <v>20226665.97773835</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1199.999999999998</v>
+      </c>
+      <c r="M3" t="n">
         <v>10800</v>
       </c>
     </row>
@@ -540,27 +584,39 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12167093.47389169</v>
+        <v>12174262.43217347</v>
       </c>
       <c r="C4" t="n">
-        <v>4927949.261446019</v>
+        <v>4929179.221952833</v>
       </c>
       <c r="D4" t="n">
-        <v>17095042.73533771</v>
+        <v>17103441.6541263</v>
       </c>
       <c r="E4" t="n">
-        <v>1119875.173830938</v>
+        <v>461.268</v>
       </c>
       <c r="F4" t="n">
-        <v>26833</v>
+        <v>17102980.3861263</v>
       </c>
       <c r="G4" t="n">
-        <v>20157946.89800121</v>
+        <v>17105289.4261263</v>
       </c>
       <c r="H4" t="n">
         <v>1200</v>
       </c>
       <c r="I4" t="n">
+        <v>1120334.433121538</v>
+      </c>
+      <c r="J4" t="n">
+        <v>26854</v>
+      </c>
+      <c r="K4" t="n">
+        <v>20124174.46335278</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1199.999999999998</v>
+      </c>
+      <c r="M4" t="n">
         <v>10800</v>
       </c>
     </row>
@@ -571,27 +627,39 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>12027825.3898224</v>
+        <v>11959426.56568014</v>
       </c>
       <c r="C5" t="n">
-        <v>16328716.24203366</v>
+        <v>16339563.4634073</v>
       </c>
       <c r="D5" t="n">
-        <v>28356541.63185607</v>
+        <v>28298990.02908744</v>
       </c>
       <c r="E5" t="n">
-        <v>3659585.916823425</v>
+        <v>461.2680000000002</v>
       </c>
       <c r="F5" t="n">
-        <v>30217</v>
+        <v>28298528.76108744</v>
       </c>
       <c r="G5" t="n">
-        <v>20028578.33176859</v>
+        <v>28300837.80108744</v>
       </c>
       <c r="H5" t="n">
         <v>1200</v>
       </c>
       <c r="I5" t="n">
+        <v>3661103.836267895</v>
+      </c>
+      <c r="J5" t="n">
+        <v>30219</v>
+      </c>
+      <c r="K5" t="n">
+        <v>19947556.62813415</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1199.999999999998</v>
+      </c>
+      <c r="M5" t="n">
         <v>10800</v>
       </c>
     </row>
@@ -602,27 +670,39 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>12127983.95869072</v>
+        <v>12138343.63163036</v>
       </c>
       <c r="C6" t="n">
-        <v>4854369.502880882</v>
+        <v>4851568.438590778</v>
       </c>
       <c r="D6" t="n">
-        <v>16982353.4615716</v>
+        <v>16989912.07022113</v>
       </c>
       <c r="E6" t="n">
-        <v>1129819.713578172</v>
+        <v>461.27031210585</v>
       </c>
       <c r="F6" t="n">
-        <v>27733</v>
+        <v>16989450.79990903</v>
       </c>
       <c r="G6" t="n">
-        <v>20077170.00368274</v>
+        <v>16991759.83990903</v>
       </c>
       <c r="H6" t="n">
-        <v>1200</v>
+        <v>1200.006015</v>
       </c>
       <c r="I6" t="n">
+        <v>1137350.264110493</v>
+      </c>
+      <c r="J6" t="n">
+        <v>27867</v>
+      </c>
+      <c r="K6" t="n">
+        <v>20062949.23088663</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1199.999999999997</v>
+      </c>
+      <c r="M6" t="n">
         <v>10800</v>
       </c>
     </row>
@@ -633,27 +713,39 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>12240126.31636273</v>
+        <v>12245259.89912461</v>
       </c>
       <c r="C7" t="n">
-        <v>4182883.694694739</v>
+        <v>4181495.102794514</v>
       </c>
       <c r="D7" t="n">
-        <v>16423010.01105747</v>
+        <v>16426755.00191913</v>
       </c>
       <c r="E7" t="n">
-        <v>977455.7298919039</v>
+        <v>461.270312105851</v>
       </c>
       <c r="F7" t="n">
-        <v>26247</v>
+        <v>16426293.73160702</v>
       </c>
       <c r="G7" t="n">
-        <v>20214858.47483939</v>
+        <v>16428602.77160702</v>
       </c>
       <c r="H7" t="n">
-        <v>1200</v>
+        <v>1200.006015000002</v>
       </c>
       <c r="I7" t="n">
+        <v>977843.894591582</v>
+      </c>
+      <c r="J7" t="n">
+        <v>26264</v>
+      </c>
+      <c r="K7" t="n">
+        <v>20174975.66734545</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1199.999999999996</v>
+      </c>
+      <c r="M7" t="n">
         <v>10800</v>
       </c>
     </row>
@@ -664,27 +756,39 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14214172.24023518</v>
+        <v>14224006.15530323</v>
       </c>
       <c r="C8" t="n">
-        <v>887662.4796349364</v>
+        <v>888861.0510265414</v>
       </c>
       <c r="D8" t="n">
-        <v>15101834.71987011</v>
+        <v>15112867.20632977</v>
       </c>
       <c r="E8" t="n">
-        <v>225377.742915506</v>
+        <v>461.268</v>
       </c>
       <c r="F8" t="n">
-        <v>9739</v>
+        <v>15112405.93832977</v>
       </c>
       <c r="G8" t="n">
-        <v>23200802.71545916</v>
+        <v>15114714.97832977</v>
       </c>
       <c r="H8" t="n">
         <v>1200</v>
       </c>
       <c r="I8" t="n">
+        <v>225506.3182033902</v>
+      </c>
+      <c r="J8" t="n">
+        <v>9741</v>
+      </c>
+      <c r="K8" t="n">
+        <v>23171655.25930667</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1199.999999999999</v>
+      </c>
+      <c r="M8" t="n">
         <v>10800</v>
       </c>
     </row>
@@ -695,27 +799,39 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14664788.18642625</v>
+        <v>14675759.06502234</v>
       </c>
       <c r="C9" t="n">
-        <v>595691.6578166978</v>
+        <v>596792.9104532594</v>
       </c>
       <c r="D9" t="n">
-        <v>15260479.84424295</v>
+        <v>15272551.9754756</v>
       </c>
       <c r="E9" t="n">
-        <v>149921.0920462913</v>
+        <v>461.268</v>
       </c>
       <c r="F9" t="n">
-        <v>6777</v>
+        <v>15272090.7074756</v>
       </c>
       <c r="G9" t="n">
-        <v>23810215.80112661</v>
+        <v>15274399.7474756</v>
       </c>
       <c r="H9" t="n">
         <v>1200</v>
       </c>
       <c r="I9" t="n">
+        <v>150001.2546771093</v>
+      </c>
+      <c r="J9" t="n">
+        <v>6778</v>
+      </c>
+      <c r="K9" t="n">
+        <v>23783897.59069154</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1199.999999999999</v>
+      </c>
+      <c r="M9" t="n">
         <v>10800</v>
       </c>
     </row>
@@ -726,27 +842,39 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>10192020.46352142</v>
+        <v>10193096.17779574</v>
       </c>
       <c r="C10" t="n">
-        <v>14748274.52081878</v>
+        <v>14738783.61310148</v>
       </c>
       <c r="D10" t="n">
-        <v>24940294.9843402</v>
+        <v>24931879.79089722</v>
       </c>
       <c r="E10" t="n">
-        <v>3363957.613861011</v>
+        <v>461.268</v>
       </c>
       <c r="F10" t="n">
-        <v>43557</v>
+        <v>24931418.52289722</v>
       </c>
       <c r="G10" t="n">
-        <v>17052230.8608738</v>
+        <v>24933727.56289722</v>
       </c>
       <c r="H10" t="n">
         <v>1200</v>
       </c>
       <c r="I10" t="n">
+        <v>3365351.369329319</v>
+      </c>
+      <c r="J10" t="n">
+        <v>43574</v>
+      </c>
+      <c r="K10" t="n">
+        <v>17007121.59756485</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1199.999999999998</v>
+      </c>
+      <c r="M10" t="n">
         <v>10800</v>
       </c>
     </row>
@@ -793,13 +921,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1168581.78613573</v>
+        <v>1168265.621828317</v>
       </c>
       <c r="C2" t="n">
-        <v>122074.6450353697</v>
+        <v>122224.7530542146</v>
       </c>
       <c r="D2" t="n">
-        <v>30274.53879712921</v>
+        <v>30467.45554478489</v>
       </c>
     </row>
     <row r="3">
@@ -809,13 +937,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1050435.663276017</v>
+        <v>1051853.131782326</v>
       </c>
       <c r="C3" t="n">
-        <v>225807.5778073889</v>
+        <v>224415.8433598015</v>
       </c>
       <c r="D3" t="n">
-        <v>53137.56108091602</v>
+        <v>52959.68941571437</v>
       </c>
     </row>
     <row r="4">
@@ -825,13 +953,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>871131.7846338504</v>
+        <v>871349.0178730288</v>
       </c>
       <c r="C4" t="n">
-        <v>240087.4914959543</v>
+        <v>240147.479607423</v>
       </c>
       <c r="D4" t="n">
-        <v>54321.10818585319</v>
+        <v>54330.01312335319</v>
       </c>
     </row>
     <row r="5">
@@ -841,13 +969,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>849359.092236487</v>
+        <v>848121.5928637978</v>
       </c>
       <c r="C5" t="n">
-        <v>374373.3589830396</v>
+        <v>375265.1989125396</v>
       </c>
       <c r="D5" t="n">
-        <v>82427.95728352771</v>
+        <v>82557.75978352773</v>
       </c>
     </row>
     <row r="6">
@@ -857,13 +985,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1097441.432522789</v>
+        <v>1096940.865530674</v>
       </c>
       <c r="C6" t="n">
-        <v>740992.4433383992</v>
+        <v>740251.828315832</v>
       </c>
       <c r="D6" t="n">
-        <v>167509.6843401399</v>
+        <v>167806.9719801709</v>
       </c>
     </row>
     <row r="7">
@@ -873,13 +1001,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1330277.806530811</v>
+        <v>1330100.784416845</v>
       </c>
       <c r="C7" t="n">
-        <v>541232.852126627</v>
+        <v>541513.7347231616</v>
       </c>
       <c r="D7" t="n">
-        <v>138095.4090821747</v>
+        <v>138092.0761200649</v>
       </c>
     </row>
     <row r="8">
@@ -889,7 +1017,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1191973.264605916</v>
+        <v>1191146.251653163</v>
       </c>
       <c r="C8" t="n">
         <v>300664.8563664798</v>
@@ -905,13 +1033,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1037639.231343358</v>
+        <v>1037672.371609916</v>
       </c>
       <c r="C9" t="n">
         <v>373068.0231965889</v>
       </c>
       <c r="D9" t="n">
-        <v>80219.0537241104</v>
+        <v>80219.05372411039</v>
       </c>
     </row>
     <row r="10">
@@ -921,13 +1049,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1008350.498346715</v>
+        <v>1009133.739051235</v>
       </c>
       <c r="C10" t="n">
-        <v>371670.8538956521</v>
+        <v>371676.4246434341</v>
       </c>
       <c r="D10" t="n">
-        <v>81319.3758796913</v>
+        <v>81332.87714050543</v>
       </c>
     </row>
     <row r="11">
@@ -937,13 +1065,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1147052.145291203</v>
+        <v>1148897.855768694</v>
       </c>
       <c r="C11" t="n">
-        <v>360221.3583227823</v>
+        <v>360232.9468686016</v>
       </c>
       <c r="D11" t="n">
-        <v>79251.62754328715</v>
+        <v>79295.36306646791</v>
       </c>
     </row>
     <row r="12">
@@ -953,13 +1081,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1498243.17920523</v>
+        <v>1500603.711454116</v>
       </c>
       <c r="C12" t="n">
-        <v>486376.5130251867</v>
+        <v>484438.7659370316</v>
       </c>
       <c r="D12" t="n">
-        <v>120049.7112381785</v>
+        <v>120850.4377354847</v>
       </c>
     </row>
   </sheetData>
@@ -1005,13 +1133,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1128958.522124066</v>
+        <v>1128641.625681626</v>
       </c>
       <c r="C2" t="n">
-        <v>398187.9682387243</v>
+        <v>398096.6264235976</v>
       </c>
       <c r="D2" t="n">
-        <v>97196.97876823971</v>
+        <v>97450.01535119281</v>
       </c>
     </row>
     <row r="3">
@@ -1021,13 +1149,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1029249.753519001</v>
+        <v>1030575.664314214</v>
       </c>
       <c r="C3" t="n">
-        <v>345584.3867617145</v>
+        <v>344384.7139086077</v>
       </c>
       <c r="D3" t="n">
-        <v>78387.87702104711</v>
+        <v>78341.09743623948</v>
       </c>
     </row>
     <row r="4">
@@ -1037,13 +1165,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>852260.1262737586</v>
+        <v>852538.7940799413</v>
       </c>
       <c r="C4" t="n">
-        <v>301791.6854482489</v>
+        <v>301851.7136319364</v>
       </c>
       <c r="D4" t="n">
-        <v>67807.16518657292</v>
+        <v>67816.07012407292</v>
       </c>
     </row>
     <row r="5">
@@ -1053,13 +1181,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>845362.7556113469</v>
+        <v>844600.4435999852</v>
       </c>
       <c r="C5" t="n">
-        <v>425295.8413249668</v>
+        <v>425675.2839442479</v>
       </c>
       <c r="D5" t="n">
-        <v>92361.62022616</v>
+        <v>92417.87978866001</v>
       </c>
     </row>
     <row r="6">
@@ -1069,13 +1197,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1087135.105114214</v>
+        <v>1087165.061258358</v>
       </c>
       <c r="C6" t="n">
-        <v>899484.9647900483</v>
+        <v>899852.332818766</v>
       </c>
       <c r="D6" t="n">
-        <v>194902.6627282431</v>
+        <v>195312.4443262991</v>
       </c>
     </row>
     <row r="7">
@@ -1085,13 +1213,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1337706.171915933</v>
+        <v>1337989.718790484</v>
       </c>
       <c r="C7" t="n">
-        <v>566817.306596966</v>
+        <v>566594.7534928079</v>
       </c>
       <c r="D7" t="n">
-        <v>142798.311078437</v>
+        <v>142788.8236727013</v>
       </c>
     </row>
     <row r="8">
@@ -1101,10 +1229,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1195452.592259624</v>
+        <v>1195292.158244862</v>
       </c>
       <c r="C8" t="n">
-        <v>309678.5644719178</v>
+        <v>309678.5644719176</v>
       </c>
       <c r="D8" t="n">
         <v>69148.44972046259</v>
@@ -1117,13 +1245,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1036068.037618321</v>
+        <v>1036713.919532411</v>
       </c>
       <c r="C9" t="n">
-        <v>402750.0665614877</v>
+        <v>402985.6785775799</v>
       </c>
       <c r="D9" t="n">
-        <v>90266.99930379329</v>
+        <v>90247.95436001074</v>
       </c>
     </row>
     <row r="10">
@@ -1133,13 +1261,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>986233.0384725753</v>
+        <v>987739.6389848781</v>
       </c>
       <c r="C10" t="n">
-        <v>507601.1490330357</v>
+        <v>507612.5524710956</v>
       </c>
       <c r="D10" t="n">
-        <v>106529.1637696464</v>
+        <v>106532.4695931165</v>
       </c>
     </row>
     <row r="11">
@@ -1149,13 +1277,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1149976.160870524</v>
+        <v>1152056.901725298</v>
       </c>
       <c r="C11" t="n">
-        <v>341096.4628637413</v>
+        <v>341810.0536577453</v>
       </c>
       <c r="D11" t="n">
-        <v>74084.85110104426</v>
+        <v>73991.26411112044</v>
       </c>
     </row>
     <row r="12">
@@ -1165,13 +1293,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1518691.210112323</v>
+        <v>1520948.505961423</v>
       </c>
       <c r="C12" t="n">
-        <v>429660.8653551679</v>
+        <v>430636.9485545326</v>
       </c>
       <c r="D12" t="n">
-        <v>106391.0949272925</v>
+        <v>106287.9646376631</v>
       </c>
     </row>
   </sheetData>
@@ -1217,13 +1345,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1376692.02367726</v>
+        <v>1376425.514682961</v>
       </c>
       <c r="C2" t="n">
-        <v>1049653.500949692</v>
+        <v>1049360.905426031</v>
       </c>
       <c r="D2" t="n">
-        <v>238277.7611577708</v>
+        <v>238346.5172559895</v>
       </c>
     </row>
     <row r="3">
@@ -1233,13 +1361,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1309560.156634329</v>
+        <v>1311804.475145889</v>
       </c>
       <c r="C3" t="n">
-        <v>710759.3465706219</v>
+        <v>710828.1857796808</v>
       </c>
       <c r="D3" t="n">
-        <v>159553.9496551107</v>
+        <v>159577.9648458659</v>
       </c>
     </row>
     <row r="4">
@@ -1249,7 +1377,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1079093.538669826</v>
+        <v>1081180.757801404</v>
       </c>
       <c r="C4" t="n">
         <v>715707.1718956959</v>
@@ -1265,7 +1393,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>934103.4131470018</v>
+        <v>933028.0630125522</v>
       </c>
       <c r="C5" t="n">
         <v>1096306.4153459</v>
@@ -1281,13 +1409,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>906837.7929451205</v>
+        <v>895946.8071697073</v>
       </c>
       <c r="C6" t="n">
-        <v>2316478.942702102</v>
+        <v>2326854.34095857</v>
       </c>
       <c r="D6" t="n">
-        <v>495705.912732719</v>
+        <v>497244.1711486145</v>
       </c>
     </row>
     <row r="7">
@@ -1297,13 +1425,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1098619.412289083</v>
+        <v>1088676.448457965</v>
       </c>
       <c r="C7" t="n">
-        <v>1937685.873374162</v>
+        <v>1939787.259393134</v>
       </c>
       <c r="D7" t="n">
-        <v>474738.5551938111</v>
+        <v>475039.7859878149</v>
       </c>
     </row>
     <row r="8">
@@ -1313,7 +1441,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1177320.558863774</v>
+        <v>1168328.177015403</v>
       </c>
       <c r="C8" t="n">
         <v>1082177.954244568</v>
@@ -1329,13 +1457,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1070586.870188957</v>
+        <v>1059518.757764196</v>
       </c>
       <c r="C9" t="n">
-        <v>837866.7482855177</v>
+        <v>838634.2483883321</v>
       </c>
       <c r="D9" t="n">
-        <v>186172.3096226031</v>
+        <v>186285.9342159859</v>
       </c>
     </row>
     <row r="10">
@@ -1345,13 +1473,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>952445.7199436086</v>
+        <v>937466.5874598298</v>
       </c>
       <c r="C10" t="n">
-        <v>1507686.004378508</v>
+        <v>1507090.563163748</v>
       </c>
       <c r="D10" t="n">
-        <v>336748.3745825619</v>
+        <v>336656.7555657271</v>
       </c>
     </row>
     <row r="11">
@@ -1361,13 +1489,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>955575.0023003587</v>
+        <v>946585.3486823023</v>
       </c>
       <c r="C11" t="n">
-        <v>2259579.978100465</v>
+        <v>2256594.481542401</v>
       </c>
       <c r="D11" t="n">
-        <v>460937.4356488529</v>
+        <v>460608.5777038959</v>
       </c>
     </row>
     <row r="12">
@@ -1377,13 +1505,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1166990.901163078</v>
+        <v>1160465.628487936</v>
       </c>
       <c r="C12" t="n">
-        <v>2814814.306186425</v>
+        <v>2816221.937269216</v>
       </c>
       <c r="D12" t="n">
-        <v>632899.3920223126</v>
+        <v>632791.9033363184</v>
       </c>
     </row>
   </sheetData>
@@ -1429,13 +1557,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1179491.308997408</v>
+        <v>1179176.493391293</v>
       </c>
       <c r="C2" t="n">
-        <v>181871.0832661276</v>
+        <v>182567.5359099733</v>
       </c>
       <c r="D2" t="n">
-        <v>45462.30338481514</v>
+        <v>45881.46191165097</v>
       </c>
     </row>
     <row r="3">
@@ -1445,13 +1573,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1027449.367464036</v>
+        <v>1029006.043394148</v>
       </c>
       <c r="C3" t="n">
-        <v>348795.023834953</v>
+        <v>347507.5398746074</v>
       </c>
       <c r="D3" t="n">
-        <v>81644.17065586694</v>
+        <v>82347.44613767117</v>
       </c>
     </row>
     <row r="4">
@@ -1461,13 +1589,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>849215.7983121702</v>
+        <v>849840.2038204418</v>
       </c>
       <c r="C4" t="n">
-        <v>305442.6143461691</v>
+        <v>305792.3472613021</v>
       </c>
       <c r="D4" t="n">
-        <v>69659.95379461371</v>
+        <v>69892.48550979474</v>
       </c>
     </row>
     <row r="5">
@@ -1477,13 +1605,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>831968.5857793087</v>
+        <v>831725.0385964166</v>
       </c>
       <c r="C5" t="n">
-        <v>434962.9953332072</v>
+        <v>435356.3301129838</v>
       </c>
       <c r="D5" t="n">
-        <v>96215.48758141769</v>
+        <v>96563.76805963914</v>
       </c>
     </row>
     <row r="6">
@@ -1493,13 +1621,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1058456.422929708</v>
+        <v>1059322.533519699</v>
       </c>
       <c r="C6" t="n">
-        <v>942277.4633637749</v>
+        <v>944010.7383521649</v>
       </c>
       <c r="D6" t="n">
-        <v>215238.6967856302</v>
+        <v>217696.522696498</v>
       </c>
     </row>
     <row r="7">
@@ -1509,13 +1637,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1335237.744834312</v>
+        <v>1336499.223886088</v>
       </c>
       <c r="C7" t="n">
-        <v>562314.0337195545</v>
+        <v>562241.4461593472</v>
       </c>
       <c r="D7" t="n">
-        <v>144329.5720733978</v>
+        <v>144701.0259329254</v>
       </c>
     </row>
     <row r="8">
@@ -1525,13 +1653,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1186733.037805029</v>
+        <v>1188074.08284323</v>
       </c>
       <c r="C8" t="n">
-        <v>314426.0700902357</v>
+        <v>313083.4870457292</v>
       </c>
       <c r="D8" t="n">
-        <v>71629.92000518019</v>
+        <v>72009.23976914486</v>
       </c>
     </row>
     <row r="9">
@@ -1541,13 +1669,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1024409.504129462</v>
+        <v>1025751.376508308</v>
       </c>
       <c r="C9" t="n">
-        <v>433421.9464657712</v>
+        <v>432831.6543418517</v>
       </c>
       <c r="D9" t="n">
-        <v>99109.45559478627</v>
+        <v>99297.97718639772</v>
       </c>
     </row>
     <row r="10">
@@ -1557,13 +1685,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>972563.6864394177</v>
+        <v>973899.9411996551</v>
       </c>
       <c r="C10" t="n">
-        <v>542825.4214098895</v>
+        <v>540766.7038114722</v>
       </c>
       <c r="D10" t="n">
-        <v>118554.1597466997</v>
+        <v>118833.9493784957</v>
       </c>
     </row>
     <row r="11">
@@ -1573,13 +1701,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1149157.922707591</v>
+        <v>1150423.949359394</v>
       </c>
       <c r="C11" t="n">
-        <v>338561.1964388487</v>
+        <v>335716.1144070833</v>
       </c>
       <c r="D11" t="n">
-        <v>75041.69288746061</v>
+        <v>75225.03539014548</v>
       </c>
     </row>
     <row r="12">
@@ -1589,13 +1717,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1513300.579292267</v>
+        <v>1514624.745111693</v>
       </c>
       <c r="C12" t="n">
-        <v>449471.6546123486</v>
+        <v>451694.5413142651</v>
       </c>
       <c r="D12" t="n">
-        <v>112934.3010683022</v>
+        <v>114901.3521381304</v>
       </c>
     </row>
   </sheetData>
@@ -1641,13 +1769,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1135940.338409413</v>
+        <v>1135614.260216728</v>
       </c>
       <c r="C2" t="n">
-        <v>208410.3456050126</v>
+        <v>208593.1388237175</v>
       </c>
       <c r="D2" t="n">
-        <v>52302.85072985249</v>
+        <v>52513.26160417597</v>
       </c>
     </row>
     <row r="3">
@@ -1657,13 +1785,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1015023.564763819</v>
+        <v>1016219.243647809</v>
       </c>
       <c r="C3" t="n">
-        <v>346179.4047837742</v>
+        <v>344606.0836978415</v>
       </c>
       <c r="D3" t="n">
-        <v>80003.14854333783</v>
+        <v>79821.47017721819</v>
       </c>
     </row>
     <row r="4">
@@ -1673,13 +1801,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>847885.3935647781</v>
+        <v>848039.7544928432</v>
       </c>
       <c r="C4" t="n">
-        <v>305194.8286815708</v>
+        <v>305007.7580008174</v>
       </c>
       <c r="D4" t="n">
-        <v>65447.42015220998</v>
+        <v>65390.73206713322</v>
       </c>
     </row>
     <row r="5">
@@ -1689,13 +1817,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>851616.9592943334</v>
+        <v>850486.7594661615</v>
       </c>
       <c r="C5" t="n">
-        <v>379032.5873283016</v>
+        <v>380225.5997072203</v>
       </c>
       <c r="D5" t="n">
-        <v>83355.07801099027</v>
+        <v>83542.08815182361</v>
       </c>
     </row>
     <row r="6">
@@ -1705,13 +1833,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1154420.9513155</v>
+        <v>1154241.724800836</v>
       </c>
       <c r="C6" t="n">
-        <v>598253.9757629964</v>
+        <v>597152.8234364811</v>
       </c>
       <c r="D6" t="n">
-        <v>137101.551861492</v>
+        <v>136820.4066412107</v>
       </c>
     </row>
     <row r="7">
@@ -1721,13 +1849,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1335243.389135955</v>
+        <v>1335318.877330786</v>
       </c>
       <c r="C7" t="n">
-        <v>516259.3610588935</v>
+        <v>516171.1743422792</v>
       </c>
       <c r="D7" t="n">
-        <v>126803.0323010644</v>
+        <v>126889.2149028311</v>
       </c>
     </row>
     <row r="8">
@@ -1737,13 +1865,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1138169.855238458</v>
+        <v>1137525.042491798</v>
       </c>
       <c r="C8" t="n">
-        <v>497120.1401080751</v>
+        <v>497563.3645302684</v>
       </c>
       <c r="D8" t="n">
-        <v>112948.6277443578</v>
+        <v>112983.6606191162</v>
       </c>
     </row>
     <row r="9">
@@ -1753,13 +1881,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1002167.923608623</v>
+        <v>1002522.877297424</v>
       </c>
       <c r="C9" t="n">
-        <v>477491.9940639504</v>
+        <v>477650.3860276719</v>
       </c>
       <c r="D9" t="n">
-        <v>112332.8424680374</v>
+        <v>112349.421557936</v>
       </c>
     </row>
     <row r="10">
@@ -1769,13 +1897,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1021219.88661719</v>
+        <v>1022444.937244444</v>
       </c>
       <c r="C10" t="n">
-        <v>311548.6276646065</v>
+        <v>311116.5597111027</v>
       </c>
       <c r="D10" t="n">
-        <v>70513.33190846433</v>
+        <v>70523.74181404909</v>
       </c>
     </row>
     <row r="11">
@@ -1785,13 +1913,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1182304.978581638</v>
+        <v>1184383.079045642</v>
       </c>
       <c r="C11" t="n">
-        <v>222168.9052529446</v>
+        <v>222347.5463064515</v>
       </c>
       <c r="D11" t="n">
-        <v>53460.49132532174</v>
+        <v>53727.20273910153</v>
       </c>
     </row>
     <row r="12">
@@ -1801,13 +1929,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1556133.075833023</v>
+        <v>1558463.343090132</v>
       </c>
       <c r="C12" t="n">
-        <v>321223.5243846167</v>
+        <v>321060.6682106635</v>
       </c>
       <c r="D12" t="n">
-        <v>83187.35484677594</v>
+        <v>83282.69431698706</v>
       </c>
     </row>
   </sheetData>
@@ -1853,13 +1981,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1296789.321893214</v>
+        <v>1296496.183737223</v>
       </c>
       <c r="C2" t="n">
-        <v>28017.74508863714</v>
+        <v>28217.49957596287</v>
       </c>
       <c r="D2" t="n">
-        <v>7155.343608439582</v>
+        <v>7236.473199426486</v>
       </c>
     </row>
     <row r="3">
@@ -1869,13 +1997,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1158714.675756972</v>
+        <v>1160283.874697595</v>
       </c>
       <c r="C3" t="n">
-        <v>67219.7899016008</v>
+        <v>67582.39239091708</v>
       </c>
       <c r="D3" t="n">
-        <v>16928.40793415853</v>
+        <v>17064.3605398813</v>
       </c>
     </row>
     <row r="4">
@@ -1885,10 +2013,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>977405.0765431829</v>
+        <v>977850.8883423093</v>
       </c>
       <c r="C4" t="n">
-        <v>51065.98523825697</v>
+        <v>51065.98523825699</v>
       </c>
       <c r="D4" t="n">
         <v>11825.22100671631</v>
@@ -1901,10 +2029,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1009308.185824804</v>
+        <v>1008621.717111215</v>
       </c>
       <c r="C5" t="n">
-        <v>99990.05890459962</v>
+        <v>99990.0589045996</v>
       </c>
       <c r="D5" t="n">
         <v>22511.87711161818</v>
@@ -1917,13 +2045,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1413976.689923734</v>
+        <v>1415362.655085051</v>
       </c>
       <c r="C6" t="n">
-        <v>155987.5966487702</v>
+        <v>157216.0631266634</v>
       </c>
       <c r="D6" t="n">
-        <v>39502.47978440135</v>
+        <v>39596.63218646208</v>
       </c>
     </row>
     <row r="7">
@@ -1933,13 +2061,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1636256.938555844</v>
+        <v>1636965.033293209</v>
       </c>
       <c r="C7" t="n">
-        <v>119125.2906957482</v>
+        <v>118846.4678298854</v>
       </c>
       <c r="D7" t="n">
-        <v>33414.03487946436</v>
+        <v>33303.06060449409</v>
       </c>
     </row>
     <row r="8">
@@ -1949,13 +2077,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1318955.938181763</v>
+        <v>1318836.972051069</v>
       </c>
       <c r="C8" t="n">
-        <v>96698.84104767593</v>
+        <v>96817.9731081888</v>
       </c>
       <c r="D8" t="n">
-        <v>23728.7769828381</v>
+        <v>23788.6526939429</v>
       </c>
     </row>
     <row r="9">
@@ -1965,7 +2093,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1188453.940467793</v>
+        <v>1189140.952384777</v>
       </c>
       <c r="C9" t="n">
         <v>81193.44186145642</v>
@@ -1981,13 +2109,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1176141.887397515</v>
+        <v>1177702.352976224</v>
       </c>
       <c r="C10" t="n">
-        <v>41615.59720854084</v>
+        <v>41214.31323696161</v>
       </c>
       <c r="D10" t="n">
-        <v>10369.16322195079</v>
+        <v>10247.56201844193</v>
       </c>
     </row>
     <row r="11">
@@ -1997,13 +2125,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1308793.97463153</v>
+        <v>1311004.363083458</v>
       </c>
       <c r="C11" t="n">
-        <v>37959.76639641621</v>
+        <v>37856.72587206915</v>
       </c>
       <c r="D11" t="n">
-        <v>9902.804684272736</v>
+        <v>9871.35245238588</v>
       </c>
     </row>
     <row r="12">
@@ -2013,13 +2141,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1729375.611058828</v>
+        <v>1731741.162541109</v>
       </c>
       <c r="C12" t="n">
-        <v>108788.3666432343</v>
+        <v>108860.1298815802</v>
       </c>
       <c r="D12" t="n">
-        <v>29289.97909755116</v>
+        <v>29311.47178592614</v>
       </c>
     </row>
   </sheetData>
@@ -2065,13 +2193,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1467039.607900827</v>
+        <v>1466752.896829321</v>
       </c>
       <c r="C2" t="n">
-        <v>12937.6697641286</v>
+        <v>12989.91452206343</v>
       </c>
       <c r="D2" t="n">
-        <v>3292.298234640745</v>
+        <v>3314.71748557158</v>
       </c>
     </row>
     <row r="3">
@@ -2081,13 +2209,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1177810.731448973</v>
+        <v>1179449.635530758</v>
       </c>
       <c r="C3" t="n">
-        <v>46726.56895632984</v>
+        <v>47174.83107074061</v>
       </c>
       <c r="D3" t="n">
-        <v>11576.35486628733</v>
+        <v>11742.11120348504</v>
       </c>
     </row>
     <row r="4">
@@ -2097,13 +2225,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>993866.6096947785</v>
+        <v>994373.8089334451</v>
       </c>
       <c r="C4" t="n">
-        <v>35830.79638415208</v>
+        <v>35830.79638415209</v>
       </c>
       <c r="D4" t="n">
-        <v>8002.691127444607</v>
+        <v>8002.691127444608</v>
       </c>
     </row>
     <row r="5">
@@ -2113,7 +2241,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1034555.641730763</v>
+        <v>1033940.792734156</v>
       </c>
       <c r="C5" t="n">
         <v>71152.89223199744</v>
@@ -2129,13 +2257,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1446113.935515594</v>
+        <v>1447620.806324835</v>
       </c>
       <c r="C6" t="n">
-        <v>112428.836226239</v>
+        <v>113683.974195528</v>
       </c>
       <c r="D6" t="n">
-        <v>28253.42318351632</v>
+        <v>28350.71732477358</v>
       </c>
     </row>
     <row r="7">
@@ -2145,13 +2273,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1687881.441704131</v>
+        <v>1688896.881007304</v>
       </c>
       <c r="C7" t="n">
-        <v>81367.80253255759</v>
+        <v>81130.38097025952</v>
       </c>
       <c r="D7" t="n">
-        <v>22636.24697252031</v>
+        <v>22541.75082832207</v>
       </c>
     </row>
     <row r="8">
@@ -2161,13 +2289,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1351556.799100679</v>
+        <v>1351659.961146005</v>
       </c>
       <c r="C8" t="n">
-        <v>63481.02438929295</v>
+        <v>63557.31984946152</v>
       </c>
       <c r="D8" t="n">
-        <v>15341.43015068692</v>
+        <v>15388.3250738086</v>
       </c>
     </row>
     <row r="9">
@@ -2177,7 +2305,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1216558.833981041</v>
+        <v>1217377.850628659</v>
       </c>
       <c r="C9" t="n">
         <v>49428.55606611645</v>
@@ -2193,13 +2321,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1200271.718976417</v>
+        <v>1201977.159788091</v>
       </c>
       <c r="C10" t="n">
-        <v>24929.27529027356</v>
+        <v>24527.99131869433</v>
       </c>
       <c r="D10" t="n">
-        <v>6203.148114395204</v>
+        <v>6081.546910886349</v>
       </c>
     </row>
     <row r="11">
@@ -2209,13 +2337,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1328134.679141744</v>
+        <v>1330356.942091711</v>
       </c>
       <c r="C11" t="n">
-        <v>22964.95723767768</v>
+        <v>22861.36523303744</v>
       </c>
       <c r="D11" t="n">
-        <v>5990.157282797268</v>
+        <v>5957.483626704581</v>
       </c>
     </row>
     <row r="12">
@@ -2225,13 +2353,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1760998.187231309</v>
+        <v>1763352.330008065</v>
       </c>
       <c r="C12" t="n">
-        <v>74443.27873793289</v>
+        <v>74454.88861120872</v>
       </c>
       <c r="D12" t="n">
-        <v>20110.48601119032</v>
+        <v>20107.05499330052</v>
       </c>
     </row>
   </sheetData>
@@ -2277,13 +2405,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>759211.0929169296</v>
+        <v>758366.6283676117</v>
       </c>
       <c r="C2" t="n">
-        <v>2461752.114180805</v>
+        <v>2461341.989425724</v>
       </c>
       <c r="D2" t="n">
-        <v>574722.964710102</v>
+        <v>574656.3380475237</v>
       </c>
     </row>
     <row r="3">
@@ -2293,13 +2421,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>875969.9575058891</v>
+        <v>876647.2714555251</v>
       </c>
       <c r="C3" t="n">
-        <v>1127685.862320058</v>
+        <v>1127122.279798831</v>
       </c>
       <c r="D3" t="n">
-        <v>251543.5797520151</v>
+        <v>251497.9970584571</v>
       </c>
     </row>
     <row r="4">
@@ -2309,7 +2437,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>746094.5188944807</v>
+        <v>745856.8207411459</v>
       </c>
       <c r="C4" t="n">
         <v>877238.4940412123</v>
@@ -2325,13 +2453,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>732358.6667812415</v>
+        <v>730602.6603872502</v>
       </c>
       <c r="C5" t="n">
-        <v>988412.2813156523</v>
+        <v>992438.1565527878</v>
       </c>
       <c r="D5" t="n">
-        <v>218490.9125336725</v>
+        <v>219085.6558875424</v>
       </c>
     </row>
     <row r="6">
@@ -2341,13 +2469,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>942356.9401053407</v>
+        <v>941877.7605272109</v>
       </c>
       <c r="C6" t="n">
-        <v>1593578.51453807</v>
+        <v>1593740.261979606</v>
       </c>
       <c r="D6" t="n">
-        <v>343315.6617562794</v>
+        <v>343348.2645016128</v>
       </c>
     </row>
     <row r="7">
@@ -2357,13 +2485,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1101456.263857264</v>
+        <v>1101193.133874638</v>
       </c>
       <c r="C7" t="n">
-        <v>1680038.912674601</v>
+        <v>1682342.900718511</v>
       </c>
       <c r="D7" t="n">
-        <v>374822.627938977</v>
+        <v>375288.9116030152</v>
       </c>
     </row>
     <row r="8">
@@ -2373,13 +2501,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>983745.4581039532</v>
+        <v>982571.9122126846</v>
       </c>
       <c r="C8" t="n">
-        <v>1290562.907475761</v>
+        <v>1289682.599581295</v>
       </c>
       <c r="D8" t="n">
-        <v>308117.087705464</v>
+        <v>307970.6395911942</v>
       </c>
     </row>
     <row r="9">
@@ -2389,13 +2517,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>775386.7900128815</v>
+        <v>775360.235643968</v>
       </c>
       <c r="C9" t="n">
-        <v>1568634.594040456</v>
+        <v>1567774.170160283</v>
       </c>
       <c r="D9" t="n">
-        <v>377984.2595123601</v>
+        <v>377856.6549129965</v>
       </c>
     </row>
     <row r="10">
@@ -2405,13 +2533,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>833512.1511797355</v>
+        <v>834506.1801427141</v>
       </c>
       <c r="C10" t="n">
-        <v>1318169.529024259</v>
+        <v>1317306.515332222</v>
       </c>
       <c r="D10" t="n">
-        <v>292976.4422161172</v>
+        <v>293052.3062386933</v>
       </c>
     </row>
     <row r="11">
@@ -2421,13 +2549,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1048442.143400044</v>
+        <v>1050369.442926066</v>
       </c>
       <c r="C11" t="n">
-        <v>889362.469152123</v>
+        <v>887387.3263903449</v>
       </c>
       <c r="D11" t="n">
-        <v>199914.9457786396</v>
+        <v>200072.2827149319</v>
       </c>
     </row>
     <row r="12">
@@ -2437,13 +2565,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1393486.480763674</v>
+        <v>1395744.131516934</v>
       </c>
       <c r="C12" t="n">
-        <v>952838.8420557731</v>
+        <v>942408.9191206638</v>
       </c>
       <c r="D12" t="n">
-        <v>229569.4648130994</v>
+        <v>230022.6516290668</v>
       </c>
     </row>
   </sheetData>
